--- a/МатПрог/lab4/Графики.xlsx
+++ b/МатПрог/lab4/Графики.xlsx
@@ -1,28 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BSTU\uni\МатПрог\lab4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BSTU\Labs\МатПрог\lab4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C8B3F21-49ED-426B-867D-72D37E274CAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92CA3BF7-4A47-4C98-B470-236590B5C3FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$B$2:$B$11</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$C$2:$C$11</definedName>
-  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -183,7 +182,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
+          <a:endParaRPr lang="ru-BY"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -491,7 +490,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="ru-RU"/>
+            <a:endParaRPr lang="ru-BY"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="378496544"/>
@@ -547,7 +546,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="ru-RU"/>
+            <a:endParaRPr lang="ru-BY"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="378497024"/>
@@ -564,7 +563,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -572,6 +570,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -595,7 +594,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="ru-RU"/>
+      <a:endParaRPr lang="ru-BY"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -852,7 +851,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="ru-RU"/>
+            <a:endParaRPr lang="ru-BY"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="424760336"/>
@@ -908,7 +907,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="ru-RU"/>
+            <a:endParaRPr lang="ru-BY"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="424749776"/>
@@ -950,13 +949,12 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
+          <a:endParaRPr lang="ru-BY"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="zero"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -964,6 +962,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -987,7 +986,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="ru-RU"/>
+      <a:endParaRPr lang="ru-BY"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -2451,16 +2450,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.28515625" customWidth="1"/>
+    <col min="1" max="1" width="21.33203125" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" customWidth="1"/>
-    <col min="5" max="5" width="26.28515625" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" customWidth="1"/>
+    <col min="4" max="4" width="16.5546875" customWidth="1"/>
+    <col min="5" max="5" width="26.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2471,7 +2470,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2491,7 +2490,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2511,7 +2510,7 @@
         <v>1.9599999999999999E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2531,7 +2530,7 @@
         <v>1.49E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2551,7 +2550,7 @@
         <v>1.46E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2571,7 +2570,7 @@
         <v>1.9400000000000001E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2591,7 +2590,7 @@
         <v>2.24E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2611,7 +2610,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2622,7 +2621,7 @@
         <v>3.9300000000000002E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2633,7 +2632,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2644,55 +2643,55 @@
         <v>3.2899999999999999E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="1"/>
     </row>
-    <row r="24" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="1"/>
     </row>
-    <row r="26" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
       <c r="D26" s="1"/>
     </row>
-    <row r="27" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="1"/>
     </row>
-    <row r="28" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="1"/>
     </row>
-    <row r="29" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
       <c r="D29" s="1"/>
     </row>
-    <row r="30" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
